--- a/data/credit_bond_2026-10-20.xlsx
+++ b/data/credit_bond_2026-10-20.xlsx
@@ -700,7 +700,11 @@
           <t>10-20 18:00</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>032680583.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -739,7 +743,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7300/1.7200</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -779,7 +783,11 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X3" s="3"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>1.89%~1.99%</t>
+        </is>
+      </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -903,7 +911,9 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="AZ3" s="3"/>
+      <c r="AZ3" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-10-20.xlsx
+++ b/data/credit_bond_2026-10-20.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-20" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-21" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>1.7300/1.7200</t>
+          <t>2.0000/1.7000</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 15.33</t>
+          <t>C- 10.71</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
@@ -776,8 +776,12 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
+      <c r="U3" s="4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
           <t>7+</t>

--- a/data/credit_bond_2026-10-20.xlsx
+++ b/data/credit_bond_2026-10-20.xlsx
@@ -719,8 +719,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>65.24</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.89</t>

--- a/data/credit_bond_2026-10-20.xlsx
+++ b/data/credit_bond_2026-10-20.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-21" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-22" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,9 @@
       <c r="E3" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>6.9</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.50</t>
@@ -757,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 10.71</t>
+          <t>C- 12.70</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">

--- a/data/credit_bond_2026-10-20.xlsx
+++ b/data/credit_bond_2026-10-20.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-22" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-23" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 12.70</t>
+          <t>C- 18.84</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="U3" s="4" t="n">
-        <v>2.55</v>
+        <v>2.5507</v>
       </c>
       <c r="V3" s="4" t="n">
         <v>2.0</v>
@@ -876,21 +876,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="AQ3" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
+      <c r="AQ3" s="3"/>
+      <c r="AR3" s="3"/>
+      <c r="AS3" s="3"/>
       <c r="AT3" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>

--- a/data/credit_bond_2026-10-20.xlsx
+++ b/data/credit_bond_2026-10-20.xlsx
@@ -876,9 +876,21 @@
           <t>7</t>
         </is>
       </c>
-      <c r="AQ3" s="3"/>
-      <c r="AR3" s="3"/>
-      <c r="AS3" s="3"/>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
       <c r="AT3" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>

--- a/data/credit_bond_2026-10-20.xlsx
+++ b/data/credit_bond_2026-10-20.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-23" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-26" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 18.84</t>
+          <t>C- 21.16</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
